--- a/artfynd/A 55774-2019 artfynd.xlsx
+++ b/artfynd/A 55774-2019 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121626084</v>
       </c>
       <c r="B2" t="n">
-        <v>56250</v>
+        <v>56251</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -809,7 +809,7 @@
         <v>121626072</v>
       </c>
       <c r="B3" t="n">
-        <v>56257</v>
+        <v>56258</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 55774-2019 artfynd.xlsx
+++ b/artfynd/A 55774-2019 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121626084</v>
+        <v>121626072</v>
       </c>
       <c r="B2" t="n">
-        <v>56251</v>
+        <v>56258</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,30 +687,30 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>205998</v>
+        <v>205992</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -806,10 +806,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121626072</v>
+        <v>121626084</v>
       </c>
       <c r="B3" t="n">
-        <v>56258</v>
+        <v>56251</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -818,30 +818,30 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>205992</v>
+        <v>205998</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>23</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
